--- a/Shiny/Datos limpios/pricing_semanal_trigo_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_trigo_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -1987,16 +1987,16 @@
         <v>45908</v>
       </c>
       <c r="D38">
-        <v>323695.9</v>
+        <v>323095.9</v>
       </c>
       <c r="E38">
-        <v>4673.79</v>
+        <v>5133.11</v>
       </c>
       <c r="F38">
         <v>6880.69</v>
       </c>
       <c r="G38">
-        <v>321489</v>
+        <v>321348.32</v>
       </c>
       <c r="H38">
         <v>46351.94</v>
@@ -2011,7 +2011,7 @@
         <v>46866.97</v>
       </c>
       <c r="L38">
-        <v>368355.97</v>
+        <v>368215.29</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2030,16 +2030,16 @@
         <v>45915</v>
       </c>
       <c r="D39">
-        <v>435871.18</v>
+        <v>435775.18</v>
       </c>
       <c r="E39">
-        <v>7163.66</v>
+        <v>7225.74</v>
       </c>
       <c r="F39">
         <v>3010.61</v>
       </c>
       <c r="G39">
-        <v>440024.23</v>
+        <v>439990.31</v>
       </c>
       <c r="H39">
         <v>81801.16</v>
@@ -2054,7 +2054,7 @@
         <v>80867.02</v>
       </c>
       <c r="L39">
-        <v>520891.25</v>
+        <v>520857.33</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2073,16 +2073,16 @@
         <v>45922</v>
       </c>
       <c r="D40">
-        <v>541014.75</v>
+        <v>539514.75</v>
       </c>
       <c r="E40">
-        <v>13320.09</v>
+        <v>14132.36</v>
       </c>
       <c r="F40">
-        <v>11319.14</v>
+        <v>11819.14</v>
       </c>
       <c r="G40">
-        <v>543015.7</v>
+        <v>541827.97</v>
       </c>
       <c r="H40">
         <v>51071.5</v>
@@ -2097,7 +2097,7 @@
         <v>51158.44</v>
       </c>
       <c r="L40">
-        <v>594174.1399999999</v>
+        <v>592986.4099999999</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2116,16 +2116,16 @@
         <v>45929</v>
       </c>
       <c r="D41">
-        <v>289002.63</v>
+        <v>284002.63</v>
       </c>
       <c r="E41">
-        <v>7354.99</v>
+        <v>11943.41</v>
       </c>
       <c r="F41">
         <v>1445.36</v>
       </c>
       <c r="G41">
-        <v>294912.26</v>
+        <v>294500.68</v>
       </c>
       <c r="H41">
         <v>40522.82</v>
@@ -2140,7 +2140,7 @@
         <v>40671.28</v>
       </c>
       <c r="L41">
-        <v>335583.54</v>
+        <v>335171.96</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2159,16 +2159,16 @@
         <v>45936</v>
       </c>
       <c r="D42">
-        <v>457425.66</v>
+        <v>457225.66</v>
       </c>
       <c r="E42">
-        <v>6785.51</v>
+        <v>6830.24</v>
       </c>
       <c r="F42">
         <v>7315.38</v>
       </c>
       <c r="G42">
-        <v>456895.79</v>
+        <v>456740.52</v>
       </c>
       <c r="H42">
         <v>32757.28</v>
@@ -2183,7 +2183,7 @@
         <v>32757.28</v>
       </c>
       <c r="L42">
-        <v>489653.0699999999</v>
+        <v>489497.7999999999</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2202,16 +2202,16 @@
         <v>45943</v>
       </c>
       <c r="D43">
-        <v>731154.48</v>
+        <v>729154.48</v>
       </c>
       <c r="E43">
-        <v>16717.91</v>
+        <v>18421.35</v>
       </c>
       <c r="F43">
         <v>4268.77</v>
       </c>
       <c r="G43">
-        <v>743603.62</v>
+        <v>743307.0599999999</v>
       </c>
       <c r="H43">
         <v>29893.04</v>
@@ -2226,7 +2226,7 @@
         <v>29993.04</v>
       </c>
       <c r="L43">
-        <v>773596.66</v>
+        <v>773300.1</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2288,33 +2288,162 @@
         <v>45957</v>
       </c>
       <c r="D45">
-        <v>960</v>
+        <v>358767.99</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>5365.76</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>5767.29</v>
       </c>
       <c r="G45">
-        <v>960</v>
+        <v>358366.46</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>43197.87</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>404.46</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>2136.56</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>41465.77</v>
       </c>
       <c r="L45">
-        <v>960</v>
+        <v>399832.23</v>
       </c>
       <c r="M45" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2025</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D46">
+        <v>359071.7</v>
+      </c>
+      <c r="E46">
+        <v>10102.47</v>
+      </c>
+      <c r="F46">
+        <v>6143.87</v>
+      </c>
+      <c r="G46">
+        <v>363030.3</v>
+      </c>
+      <c r="H46">
+        <v>42976.97</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>480</v>
+      </c>
+      <c r="K46">
+        <v>42496.97</v>
+      </c>
+      <c r="L46">
+        <v>405527.27</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2025</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D47">
+        <v>542530.45</v>
+      </c>
+      <c r="E47">
+        <v>3178.69</v>
+      </c>
+      <c r="F47">
+        <v>7871.59</v>
+      </c>
+      <c r="G47">
+        <v>537837.5499999999</v>
+      </c>
+      <c r="H47">
+        <v>62725.96</v>
+      </c>
+      <c r="I47">
+        <v>388.53</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>63114.49</v>
+      </c>
+      <c r="L47">
+        <v>600952.0399999999</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2025</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D48">
+        <v>449503.07</v>
+      </c>
+      <c r="E48">
+        <v>6098.1</v>
+      </c>
+      <c r="F48">
+        <v>7454</v>
+      </c>
+      <c r="G48">
+        <v>448147.17</v>
+      </c>
+      <c r="H48">
+        <v>39276.31</v>
+      </c>
+      <c r="I48">
+        <v>249.67</v>
+      </c>
+      <c r="J48">
+        <v>330</v>
+      </c>
+      <c r="K48">
+        <v>39195.98</v>
+      </c>
+      <c r="L48">
+        <v>487343.15</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>TRIGO</t>
         </is>
